--- a/Server/婚礼细节.xlsx
+++ b/Server/婚礼细节.xlsx
@@ -27,9 +27,60 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="18">
   <si>
     <t>婚礼细节；</t>
+  </si>
+  <si>
+    <t>项目</t>
+  </si>
+  <si>
+    <t>时间点</t>
+  </si>
+  <si>
+    <t>进度</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>化妆</t>
+  </si>
+  <si>
+    <t>2026.2.10</t>
+  </si>
+  <si>
+    <t>未完成</t>
+  </si>
+  <si>
+    <t>上门化妆</t>
+  </si>
+  <si>
+    <t>摄影跟拍</t>
+  </si>
+  <si>
+    <t>和化妆一起，从开始化妆就开始拍摄</t>
+  </si>
+  <si>
+    <t>三桃结亲</t>
+  </si>
+  <si>
+    <t>下午去三桃，住一晚上，第二天(2026.2.11)早上吃完饭回威信</t>
+  </si>
+  <si>
+    <t>结亲回家</t>
+  </si>
+  <si>
+    <t>2026.2.11</t>
+  </si>
+  <si>
+    <t>不去酒店，直接回家，然后再去酒店，时间在12点左右</t>
+  </si>
+  <si>
+    <t>在酒店</t>
+  </si>
+  <si>
+    <t>司仪致辞-&gt;新郎新娘入场-&gt;回答誓言(我愿意)-&gt;交换戒指-&gt;致谢-&gt;合影</t>
   </si>
 </sst>
 </file>
@@ -645,8 +696,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1174,12 +1228,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="8.88888888888889" defaultRowHeight="14.4" outlineLevelRow="6" outlineLevelCol="4"/>
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="2:5">
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5">
+      <c r="B3" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5">
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5">
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" t="s">
+        <v>6</v>
+      </c>
+      <c r="D5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5">
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5">
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
